--- a/doc/PatPet_WBS_개발일정.xlsx
+++ b/doc/PatPet_WBS_개발일정.xlsx
@@ -600,7 +600,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>■ 프로젝트 기간: 2026.08.03 ~ 2026.09.09 (주말 제외)</t>
+          <t>■ 프로젝트 기간: 2026.08.03 ~ 2026.09.09 (주말 및 법정 공휴일 8/17 제외)</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       <c r="T6" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="U6" s="9" t="n">
+      <c r="U6" s="10" t="n">
         <v>17</v>
       </c>
       <c r="V6" s="9" t="n">
@@ -866,9 +866,9 @@
           <t>일</t>
         </is>
       </c>
-      <c r="U7" s="9" t="inlineStr">
-        <is>
-          <t>월</t>
+      <c r="U7" s="10" t="inlineStr">
+        <is>
+          <t>월(휴)</t>
         </is>
       </c>
       <c r="V7" s="9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       <c r="R8" s="14" t="n"/>
       <c r="S8" s="15" t="n"/>
       <c r="T8" s="15" t="n"/>
-      <c r="U8" s="14" t="n"/>
+      <c r="U8" s="15" t="n"/>
       <c r="V8" s="14" t="n"/>
       <c r="W8" s="14" t="n"/>
       <c r="X8" s="14" t="n"/>
@@ -1102,7 +1102,7 @@
       <c r="R9" s="14" t="n"/>
       <c r="S9" s="15" t="n"/>
       <c r="T9" s="15" t="n"/>
-      <c r="U9" s="14" t="n"/>
+      <c r="U9" s="15" t="n"/>
       <c r="V9" s="14" t="n"/>
       <c r="W9" s="14" t="n"/>
       <c r="X9" s="14" t="n"/>
@@ -1172,7 +1172,7 @@
       <c r="R10" s="14" t="n"/>
       <c r="S10" s="15" t="n"/>
       <c r="T10" s="15" t="n"/>
-      <c r="U10" s="14" t="n"/>
+      <c r="U10" s="15" t="n"/>
       <c r="V10" s="14" t="n"/>
       <c r="W10" s="14" t="n"/>
       <c r="X10" s="14" t="n"/>
@@ -1242,7 +1242,7 @@
       <c r="R11" s="14" t="n"/>
       <c r="S11" s="15" t="n"/>
       <c r="T11" s="15" t="n"/>
-      <c r="U11" s="14" t="n"/>
+      <c r="U11" s="15" t="n"/>
       <c r="V11" s="14" t="n"/>
       <c r="W11" s="14" t="n"/>
       <c r="X11" s="14" t="n"/>
@@ -1312,7 +1312,7 @@
       <c r="R12" s="14" t="n"/>
       <c r="S12" s="15" t="n"/>
       <c r="T12" s="15" t="n"/>
-      <c r="U12" s="14" t="n"/>
+      <c r="U12" s="15" t="n"/>
       <c r="V12" s="14" t="n"/>
       <c r="W12" s="14" t="n"/>
       <c r="X12" s="14" t="n"/>
@@ -1382,7 +1382,7 @@
       <c r="R13" s="14" t="n"/>
       <c r="S13" s="15" t="n"/>
       <c r="T13" s="15" t="n"/>
-      <c r="U13" s="14" t="n"/>
+      <c r="U13" s="15" t="n"/>
       <c r="V13" s="14" t="n"/>
       <c r="W13" s="14" t="n"/>
       <c r="X13" s="14" t="n"/>
@@ -1452,7 +1452,7 @@
       <c r="R14" s="14" t="n"/>
       <c r="S14" s="15" t="n"/>
       <c r="T14" s="15" t="n"/>
-      <c r="U14" s="14" t="n"/>
+      <c r="U14" s="15" t="n"/>
       <c r="V14" s="14" t="n"/>
       <c r="W14" s="14" t="n"/>
       <c r="X14" s="14" t="n"/>
@@ -1522,7 +1522,7 @@
       <c r="R15" s="17" t="n"/>
       <c r="S15" s="15" t="n"/>
       <c r="T15" s="15" t="n"/>
-      <c r="U15" s="17" t="n"/>
+      <c r="U15" s="15" t="n"/>
       <c r="V15" s="17" t="n"/>
       <c r="W15" s="14" t="n"/>
       <c r="X15" s="14" t="n"/>
@@ -1592,7 +1592,7 @@
       <c r="R16" s="16" t="n"/>
       <c r="S16" s="15" t="n"/>
       <c r="T16" s="15" t="n"/>
-      <c r="U16" s="16" t="n"/>
+      <c r="U16" s="15" t="n"/>
       <c r="V16" s="16" t="n"/>
       <c r="W16" s="14" t="n"/>
       <c r="X16" s="14" t="n"/>
@@ -1662,7 +1662,7 @@
       <c r="R17" s="14" t="n"/>
       <c r="S17" s="15" t="n"/>
       <c r="T17" s="15" t="n"/>
-      <c r="U17" s="14" t="n"/>
+      <c r="U17" s="15" t="n"/>
       <c r="V17" s="17" t="n"/>
       <c r="W17" s="17" t="n"/>
       <c r="X17" s="17" t="n"/>
@@ -1732,7 +1732,7 @@
       <c r="R18" s="14" t="n"/>
       <c r="S18" s="15" t="n"/>
       <c r="T18" s="15" t="n"/>
-      <c r="U18" s="14" t="n"/>
+      <c r="U18" s="15" t="n"/>
       <c r="V18" s="14" t="n"/>
       <c r="W18" s="16" t="n"/>
       <c r="X18" s="16" t="n"/>
@@ -1802,7 +1802,7 @@
       <c r="R19" s="18" t="n"/>
       <c r="S19" s="15" t="n"/>
       <c r="T19" s="15" t="n"/>
-      <c r="U19" s="18" t="n"/>
+      <c r="U19" s="15" t="n"/>
       <c r="V19" s="18" t="n"/>
       <c r="W19" s="14" t="n"/>
       <c r="X19" s="14" t="n"/>
@@ -1872,7 +1872,7 @@
       <c r="R20" s="14" t="n"/>
       <c r="S20" s="15" t="n"/>
       <c r="T20" s="15" t="n"/>
-      <c r="U20" s="14" t="n"/>
+      <c r="U20" s="15" t="n"/>
       <c r="V20" s="14" t="n"/>
       <c r="W20" s="18" t="n"/>
       <c r="X20" s="18" t="n"/>
@@ -1942,7 +1942,7 @@
       <c r="R21" s="14" t="n"/>
       <c r="S21" s="15" t="n"/>
       <c r="T21" s="15" t="n"/>
-      <c r="U21" s="14" t="n"/>
+      <c r="U21" s="15" t="n"/>
       <c r="V21" s="14" t="n"/>
       <c r="W21" s="14" t="n"/>
       <c r="X21" s="14" t="n"/>
@@ -2012,7 +2012,7 @@
       <c r="R22" s="14" t="n"/>
       <c r="S22" s="15" t="n"/>
       <c r="T22" s="15" t="n"/>
-      <c r="U22" s="14" t="n"/>
+      <c r="U22" s="15" t="n"/>
       <c r="V22" s="14" t="n"/>
       <c r="W22" s="14" t="n"/>
       <c r="X22" s="14" t="n"/>
@@ -2082,7 +2082,7 @@
       <c r="R23" s="14" t="n"/>
       <c r="S23" s="15" t="n"/>
       <c r="T23" s="15" t="n"/>
-      <c r="U23" s="14" t="n"/>
+      <c r="U23" s="15" t="n"/>
       <c r="V23" s="14" t="n"/>
       <c r="W23" s="14" t="n"/>
       <c r="X23" s="14" t="n"/>
@@ -2152,7 +2152,7 @@
       <c r="R24" s="14" t="n"/>
       <c r="S24" s="15" t="n"/>
       <c r="T24" s="15" t="n"/>
-      <c r="U24" s="14" t="n"/>
+      <c r="U24" s="15" t="n"/>
       <c r="V24" s="14" t="n"/>
       <c r="W24" s="14" t="n"/>
       <c r="X24" s="14" t="n"/>
@@ -2222,7 +2222,7 @@
       <c r="R25" s="14" t="n"/>
       <c r="S25" s="15" t="n"/>
       <c r="T25" s="15" t="n"/>
-      <c r="U25" s="14" t="n"/>
+      <c r="U25" s="15" t="n"/>
       <c r="V25" s="14" t="n"/>
       <c r="W25" s="14" t="n"/>
       <c r="X25" s="14" t="n"/>
@@ -2292,7 +2292,7 @@
       <c r="R26" s="14" t="n"/>
       <c r="S26" s="15" t="n"/>
       <c r="T26" s="15" t="n"/>
-      <c r="U26" s="14" t="n"/>
+      <c r="U26" s="15" t="n"/>
       <c r="V26" s="14" t="n"/>
       <c r="W26" s="14" t="n"/>
       <c r="X26" s="14" t="n"/>
@@ -2362,7 +2362,7 @@
       <c r="R27" s="14" t="n"/>
       <c r="S27" s="15" t="n"/>
       <c r="T27" s="15" t="n"/>
-      <c r="U27" s="14" t="n"/>
+      <c r="U27" s="15" t="n"/>
       <c r="V27" s="14" t="n"/>
       <c r="W27" s="14" t="n"/>
       <c r="X27" s="14" t="n"/>
@@ -2432,7 +2432,7 @@
       <c r="R28" s="14" t="n"/>
       <c r="S28" s="15" t="n"/>
       <c r="T28" s="15" t="n"/>
-      <c r="U28" s="14" t="n"/>
+      <c r="U28" s="15" t="n"/>
       <c r="V28" s="14" t="n"/>
       <c r="W28" s="14" t="n"/>
       <c r="X28" s="14" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="R29" s="14" t="n"/>
       <c r="S29" s="15" t="n"/>
       <c r="T29" s="15" t="n"/>
-      <c r="U29" s="14" t="n"/>
+      <c r="U29" s="15" t="n"/>
       <c r="V29" s="14" t="n"/>
       <c r="W29" s="14" t="n"/>
       <c r="X29" s="14" t="n"/>
@@ -2572,7 +2572,7 @@
       <c r="R30" s="14" t="n"/>
       <c r="S30" s="15" t="n"/>
       <c r="T30" s="15" t="n"/>
-      <c r="U30" s="14" t="n"/>
+      <c r="U30" s="15" t="n"/>
       <c r="V30" s="14" t="n"/>
       <c r="W30" s="14" t="n"/>
       <c r="X30" s="14" t="n"/>
@@ -2642,7 +2642,7 @@
       <c r="R31" s="14" t="n"/>
       <c r="S31" s="15" t="n"/>
       <c r="T31" s="15" t="n"/>
-      <c r="U31" s="14" t="n"/>
+      <c r="U31" s="15" t="n"/>
       <c r="V31" s="14" t="n"/>
       <c r="W31" s="14" t="n"/>
       <c r="X31" s="14" t="n"/>
@@ -2712,7 +2712,7 @@
       <c r="R32" s="14" t="n"/>
       <c r="S32" s="15" t="n"/>
       <c r="T32" s="15" t="n"/>
-      <c r="U32" s="14" t="n"/>
+      <c r="U32" s="15" t="n"/>
       <c r="V32" s="14" t="n"/>
       <c r="W32" s="14" t="n"/>
       <c r="X32" s="14" t="n"/>
@@ -2782,7 +2782,7 @@
       <c r="R33" s="14" t="n"/>
       <c r="S33" s="15" t="n"/>
       <c r="T33" s="15" t="n"/>
-      <c r="U33" s="14" t="n"/>
+      <c r="U33" s="15" t="n"/>
       <c r="V33" s="14" t="n"/>
       <c r="W33" s="14" t="n"/>
       <c r="X33" s="14" t="n"/>
@@ -2852,7 +2852,7 @@
       <c r="R34" s="14" t="n"/>
       <c r="S34" s="15" t="n"/>
       <c r="T34" s="15" t="n"/>
-      <c r="U34" s="14" t="n"/>
+      <c r="U34" s="15" t="n"/>
       <c r="V34" s="14" t="n"/>
       <c r="W34" s="14" t="n"/>
       <c r="X34" s="14" t="n"/>
@@ -2922,7 +2922,7 @@
       <c r="R35" s="14" t="n"/>
       <c r="S35" s="15" t="n"/>
       <c r="T35" s="15" t="n"/>
-      <c r="U35" s="14" t="n"/>
+      <c r="U35" s="15" t="n"/>
       <c r="V35" s="14" t="n"/>
       <c r="W35" s="14" t="n"/>
       <c r="X35" s="14" t="n"/>
@@ -2992,7 +2992,7 @@
       <c r="R36" s="14" t="n"/>
       <c r="S36" s="15" t="n"/>
       <c r="T36" s="15" t="n"/>
-      <c r="U36" s="14" t="n"/>
+      <c r="U36" s="15" t="n"/>
       <c r="V36" s="14" t="n"/>
       <c r="W36" s="14" t="n"/>
       <c r="X36" s="14" t="n"/>

--- a/doc/PatPet_WBS_개발일정.xlsx
+++ b/doc/PatPet_WBS_개발일정.xlsx
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>[PetPulse] 반려동물 AI 헬스케어 플랫폼 개발일정 (WBS)</t>
+          <t>[PatPet] 반려동물 AI 헬스케어 플랫폼 개발일정 (WBS)</t>
         </is>
       </c>
     </row>
